--- a/public/exports-60-250-with-coowners/29189900.xlsx
+++ b/public/exports-60-250-with-coowners/29189900.xlsx
@@ -5164,7 +5164,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056978</t>
+          <t xml:space="preserve">200056974</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914896</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
